--- a/test_data/WTA/WTA Pillar2 Menu/WTA Pillar2 Menu_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Menu/WTA Pillar2 Menu_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,35 +512,274 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>P2Menu_01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Menu</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>The Pillar 2 dropdown lists exactly its 7 known items</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Opening the 'Pillar 2' nav dropdown must show Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation and News - no more, no less.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Open the 'Pillar 2' dropdown
+3. Verify each of the 7 items is visible</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Opening the 'Pillar 2' nav dropdown must show Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation and News - no more, no less.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>The Pillar 2 dropdown showed all 7 expected items: Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation, News.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] All 7 Pillar 2 dropdown items are visible</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>P2Menu_02_Information</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Menu</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Pillar 2 &gt; Information navigates to its page</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Information' in the Pillar 2 dropdown must navigate to /wta/PillarTwoInformation.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Menu item: Information</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Open the Pillar 2 dropdown
+3. Click 'Information'
+4. Verify the URL contains /wta/PillarTwoInformation</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Information' in the Pillar 2 dropdown must navigate to /wta/PillarTwoInformation.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Information' navigated to https://regplus.kaz.com.bd/wta/PillarTwoInformation.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/PillarTwoInformation</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P2Menu_03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Menu</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>'Simulator' navigates out of the WTA module to the P2 Simulator workspace</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Simulator' in the Pillar 2 dropdown must navigate to /companydata/P2Simulator/, a different product area (Transfer Pricing Analyzer's 'Master Entity Chart'), not a page under /wta/.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Open the Pillar 2 dropdown
+3. Click 'Simulator'
+4. Verify the URL is /companydata/P2Simulator/</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Simulator' in the Pillar 2 dropdown must navigate to /companydata/P2Simulator/, a different product area (Transfer Pricing Analyzer's 'Master Entity Chart'), not a page under /wta/.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Simulator' navigated to https://regplus.kaz.com.bd/companydata/P2Simulator/, outside the /wta/ module as expected.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /companydata/P2Simulator</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P2Menu_02_ComplianceCalendar</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Menu</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Pillar 2 &gt; Compliance Calendar navigates to its page</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Compliance Calendar' in the Pillar 2 dropdown must navigate to /wta/ComplianceCalendar.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Menu item: Compliance Calendar</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Open the Pillar 2 dropdown
+3. Click 'Compliance Calendar'
+4. Verify the URL contains /wta/ComplianceCalendar</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Compliance Calendar' in the Pillar 2 dropdown must navigate to /wta/ComplianceCalendar.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Compliance Calendar' navigated to https://regplus.kaz.com.bd/wta/ComplianceCalendar.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/ComplianceCalendar</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>P2Menu_02_Forms</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Pillar 2 &gt; Forms navigates to its page</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Forms' in the Pillar 2 dropdown must navigate to /wta/PillarTwoForms.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Menu item: Forms</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -548,59 +787,59 @@
 4. Verify the URL contains /wta/PillarTwoForms</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Forms' in the Pillar 2 dropdown must navigate to /wta/PillarTwoForms.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Forms' navigated to https://regplus.reganalytics.com/wta/PillarTwoForms.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/PillarTwoForms.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/PillarTwoForms</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>P2Menu_02_CountryCommentary</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Pillar 2 &gt; Country Commentary navigates to its page</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Country Commentary' in the Pillar 2 dropdown must navigate to /wta/CountryCommentary.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Menu item: Country Commentary</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -608,22 +847,142 @@
 4. Verify the URL contains /wta/CountryCommentary</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Country Commentary' in the Pillar 2 dropdown must navigate to /wta/CountryCommentary.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Country Commentary' navigated to https://regplus.reganalytics.com/wta/CountryCommentary.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Country Commentary' navigated to https://regplus.kaz.com.bd/wta/CountryCommentary.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/CountryCommentary</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P2Menu_02_Regulation</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Menu</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Pillar 2 &gt; Regulation navigates to its page</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulation' in the Pillar 2 dropdown must navigate to /wta/PillarTwoRegulation.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Menu item: Regulation</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Open the Pillar 2 dropdown
+3. Click 'Regulation'
+4. Verify the URL contains /wta/PillarTwoRegulation</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulation' in the Pillar 2 dropdown must navigate to /wta/PillarTwoRegulation.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulation' navigated to https://regplus.kaz.com.bd/wta/PillarTwoRegulation.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/PillarTwoRegulation</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>P2Menu_02_News</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 Menu</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Pillar 2 &gt; News navigates to its page</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'News' in the Pillar 2 dropdown must navigate to /wta/PillarTwoNews.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Menu item: News</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Open the Pillar 2 dropdown
+3. Click 'News'
+4. Verify the URL contains /wta/PillarTwoNews</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'News' in the Pillar 2 dropdown must navigate to /wta/PillarTwoNews.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/PillarTwoNews.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/PillarTwoNews</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 Menu/WTA Pillar2 Menu_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Menu/WTA Pillar2 Menu_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Menu_01</t>
+          <t>P2Menu_02_Information</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The Pillar 2 dropdown lists exactly its 7 known items</t>
+          <t>Pillar 2 &gt; Information navigates to its page</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Opening the 'Pillar 2' nav dropdown must show Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation and News - no more, no less.</t>
+          <t>Clicking 'Information' in the Pillar 2 dropdown must navigate to /wta/PillarTwoInformation.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -537,69 +537,10 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Menu item: Information</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the 'Pillar 2' dropdown
-3. Verify each of the 7 items is visible</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Opening the 'Pillar 2' nav dropdown must show Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation and News - no more, no less.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>The Pillar 2 dropdown showed all 7 expected items: Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation, News.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 7 Pillar 2 dropdown items are visible</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P2Menu_02_Information</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Menu</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Pillar 2 &gt; Information navigates to its page</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Information' in the Pillar 2 dropdown must navigate to /wta/PillarTwoInformation.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Information</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -607,59 +548,59 @@
 4. Verify the URL contains /wta/PillarTwoInformation</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Information' in the Pillar 2 dropdown must navigate to /wta/PillarTwoInformation.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Information' navigated to https://regplus.kaz.com.bd/wta/PillarTwoInformation.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Information' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoInformation.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/PillarTwoInformation</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>P2Menu_03</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>'Simulator' navigates out of the WTA module to the P2 Simulator workspace</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Simulator' in the Pillar 2 dropdown must navigate to /companydata/P2Simulator/, a different product area (Transfer Pricing Analyzer's 'Master Entity Chart'), not a page under /wta/.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -667,59 +608,59 @@
 4. Verify the URL is /companydata/P2Simulator/</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Simulator' in the Pillar 2 dropdown must navigate to /companydata/P2Simulator/, a different product area (Transfer Pricing Analyzer's 'Master Entity Chart'), not a page under /wta/.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Simulator' navigated to https://regplus.kaz.com.bd/companydata/P2Simulator/, outside the /wta/ module as expected.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Simulator' navigated to https://regplusrc.reganalytics.com/companydata/P2Simulator/, outside the /wta/ module as expected.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /companydata/P2Simulator</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>P2Menu_02_ComplianceCalendar</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Pillar 2 &gt; Compliance Calendar navigates to its page</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Compliance Calendar' in the Pillar 2 dropdown must navigate to /wta/ComplianceCalendar.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Menu item: Compliance Calendar</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -727,59 +668,59 @@
 4. Verify the URL contains /wta/ComplianceCalendar</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Compliance Calendar' in the Pillar 2 dropdown must navigate to /wta/ComplianceCalendar.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Compliance Calendar' navigated to https://regplus.kaz.com.bd/wta/ComplianceCalendar.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Compliance Calendar' navigated to https://regplusrc.reganalytics.com/wta/ComplianceCalendar.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/ComplianceCalendar</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>P2Menu_02_Forms</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Pillar 2 &gt; Forms navigates to its page</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Forms' in the Pillar 2 dropdown must navigate to /wta/PillarTwoForms.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Menu item: Forms</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -787,59 +728,59 @@
 4. Verify the URL contains /wta/PillarTwoForms</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Forms' in the Pillar 2 dropdown must navigate to /wta/PillarTwoForms.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Forms' navigated to https://regplus.kaz.com.bd/wta/PillarTwoForms.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Forms' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoForms.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/PillarTwoForms</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>P2Menu_02_CountryCommentary</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Pillar 2 &gt; Country Commentary navigates to its page</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Country Commentary' in the Pillar 2 dropdown must navigate to /wta/CountryCommentary.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Menu item: Country Commentary</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -847,59 +788,59 @@
 4. Verify the URL contains /wta/CountryCommentary</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Country Commentary' in the Pillar 2 dropdown must navigate to /wta/CountryCommentary.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Country Commentary' navigated to https://regplus.kaz.com.bd/wta/CountryCommentary.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Country Commentary' navigated to https://regplusrc.reganalytics.com/wta/CountryCommentary.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/CountryCommentary</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>P2Menu_02_Regulation</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Pillar 2 &gt; Regulation navigates to its page</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Regulation' in the Pillar 2 dropdown must navigate to /wta/PillarTwoRegulation.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Menu item: Regulation</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -907,59 +848,59 @@
 4. Verify the URL contains /wta/PillarTwoRegulation</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Regulation' in the Pillar 2 dropdown must navigate to /wta/PillarTwoRegulation.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Regulation' navigated to https://regplus.kaz.com.bd/wta/PillarTwoRegulation.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Regulation' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoRegulation.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/PillarTwoRegulation</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>P2Menu_02_News</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 Menu</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Pillar 2 &gt; News navigates to its page</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Clicking 'News' in the Pillar 2 dropdown must navigate to /wta/PillarTwoNews.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Menu item: News</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Pillar 2 dropdown
@@ -967,22 +908,22 @@
 4. Verify the URL contains /wta/PillarTwoNews</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Clicking 'News' in the Pillar 2 dropdown must navigate to /wta/PillarTwoNews.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' navigated to https://regplus.kaz.com.bd/wta/PillarTwoNews.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'News' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoNews.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/PillarTwoNews</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 Menu/WTA Pillar2 Menu_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 Menu/WTA Pillar2 Menu_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2Menu_02_Information</t>
+          <t>P2Menu_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; Information navigates to its page</t>
+          <t>The Pillar 2 dropdown lists exactly its 7 known items</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Information' in the Pillar 2 dropdown must navigate to /wta/PillarTwoInformation.</t>
+          <t>Opening the 'Pillar 2' nav dropdown must show Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation and News - no more, no less.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -537,393 +537,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Menu item: Information</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Open the Pillar 2 dropdown
-3. Click 'Information'
-4. Verify the URL contains /wta/PillarTwoInformation</t>
+2. Open the 'Pillar 2' dropdown
+3. Verify each of the 7 items is visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Information' in the Pillar 2 dropdown must navigate to /wta/PillarTwoInformation.</t>
+          <t>Opening the 'Pillar 2' nav dropdown must show Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation and News - no more, no less.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Information' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoInformation.</t>
+          <t>The Pillar 2 dropdown showed all 7 expected items: Information, Compliance Calendar, Forms, Simulator, Country Commentary, Regulation, News.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL contains /wta/PillarTwoInformation</t>
+          <t>[PASS] All 7 Pillar 2 dropdown items are visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P2Menu_03</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Menu</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>'Simulator' navigates out of the WTA module to the P2 Simulator workspace</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Simulator' in the Pillar 2 dropdown must navigate to /companydata/P2Simulator/, a different product area (Transfer Pricing Analyzer's 'Master Entity Chart'), not a page under /wta/.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Pillar 2 dropdown
-3. Click 'Simulator'
-4. Verify the URL is /companydata/P2Simulator/</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Simulator' in the Pillar 2 dropdown must navigate to /companydata/P2Simulator/, a different product area (Transfer Pricing Analyzer's 'Master Entity Chart'), not a page under /wta/.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Simulator' navigated to https://regplusrc.reganalytics.com/companydata/P2Simulator/, outside the /wta/ module as expected.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /companydata/P2Simulator</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2Menu_02_ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Menu</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Pillar 2 &gt; Compliance Calendar navigates to its page</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Compliance Calendar' in the Pillar 2 dropdown must navigate to /wta/ComplianceCalendar.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Compliance Calendar</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Pillar 2 dropdown
-3. Click 'Compliance Calendar'
-4. Verify the URL contains /wta/ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Compliance Calendar' in the Pillar 2 dropdown must navigate to /wta/ComplianceCalendar.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Compliance Calendar' navigated to https://regplusrc.reganalytics.com/wta/ComplianceCalendar.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/ComplianceCalendar</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2Menu_02_Forms</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Menu</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Pillar 2 &gt; Forms navigates to its page</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Forms' in the Pillar 2 dropdown must navigate to /wta/PillarTwoForms.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Forms</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Pillar 2 dropdown
-3. Click 'Forms'
-4. Verify the URL contains /wta/PillarTwoForms</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Forms' in the Pillar 2 dropdown must navigate to /wta/PillarTwoForms.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Forms' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoForms.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/PillarTwoForms</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P2Menu_02_CountryCommentary</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Menu</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Pillar 2 &gt; Country Commentary navigates to its page</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Country Commentary' in the Pillar 2 dropdown must navigate to /wta/CountryCommentary.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Country Commentary</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Pillar 2 dropdown
-3. Click 'Country Commentary'
-4. Verify the URL contains /wta/CountryCommentary</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Country Commentary' in the Pillar 2 dropdown must navigate to /wta/CountryCommentary.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Country Commentary' navigated to https://regplusrc.reganalytics.com/wta/CountryCommentary.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/CountryCommentary</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P2Menu_02_Regulation</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Menu</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Pillar 2 &gt; Regulation navigates to its page</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Regulation' in the Pillar 2 dropdown must navigate to /wta/PillarTwoRegulation.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Regulation</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Pillar 2 dropdown
-3. Click 'Regulation'
-4. Verify the URL contains /wta/PillarTwoRegulation</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Regulation' in the Pillar 2 dropdown must navigate to /wta/PillarTwoRegulation.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Regulation' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoRegulation.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/PillarTwoRegulation</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P2Menu_02_News</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 Menu</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Pillar 2 &gt; News navigates to its page</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' in the Pillar 2 dropdown must navigate to /wta/PillarTwoNews.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: News</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Pillar 2 dropdown
-3. Click 'News'
-4. Verify the URL contains /wta/PillarTwoNews</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' in the Pillar 2 dropdown must navigate to /wta/PillarTwoNews.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'News' navigated to https://regplusrc.reganalytics.com/wta/PillarTwoNews.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/PillarTwoNews</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
